--- a/deliverables/exports/track-b/01-service-offer-matrix.xlsx
+++ b/deliverables/exports/track-b/01-service-offer-matrix.xlsx
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>A short self assessment that scores a builder on the six things a North American buyer checks before awarding work, and returns a per dimension breakdown rather than a single verdict</t>
+          <t>A short self assessment scoring a builder on six evidenced dimensions from 00-BUYER-CHECKS.md, returning a per dimension breakdown and a band position rather than a single verdict</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>A low score on legibility is not solvable by getting better at building, which is what this audience does when a deal is lost. It is solvable by learning what the buyer checks and how to show it. That is the offer</t>
+          <t>A low score is not solvable by getting better at building, which is what this audience does when a deal is lost. Part of it is solvable by presenting differently and part of it has to be built. Knowing which is which is the offer, per 00-RESOLUTIONS.md conflict 3</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Direct. ICP Level 1 in Phase 4, can build, no target market revenue yet</t>
+          <t>Direct. ICP Level 1 in Phase 4, can build, no target market revenue yet. The band result is what routes Level 1 and Level 2 differently</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -2220,46 +2220,58 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>One to one delivery ceiling</t>
+          <t>The walkthroughs now have evidenced content</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Phase 9 anchor tier and slot caps</t>
+          <t>00-BUYER-CHECKS.md supplies what was previously an empty differentiator</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Courses are commodity, free supply sets the ceiling at zero</t>
+          <t>One to one delivery ceiling</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Phase 3 positioning against free content. Phase 9 floor</t>
+          <t>Phase 9 anchor tier and slot caps</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Buyer Readiness Scorecard</t>
+          <t>Courses are commodity, free supply sets the ceiling at zero</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Phase 8 top of funnel, all three channels. The lead magnet spec</t>
+          <t>Phase 3 positioning against free content. Phase 9 floor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>Buyer Readiness Scorecard</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Phase 8 top of funnel, all three channels. The lead magnet spec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>Build order, item 8 before item 5</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Phase 8 sequencing</t>
         </is>
